--- a/artfynd/A 37930-2021 artfynd.xlsx
+++ b/artfynd/A 37930-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37930-2021 artfynd.xlsx
+++ b/artfynd/A 37930-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>585329</v>
+        <v>89256815</v>
       </c>
       <c r="B2" t="n">
-        <v>102160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1560</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rumskulla, 600 m N om kyrkan, Sm</t>
+          <t>1 km N Rumskulla (Bv2020_S14), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535572.3250552899</v>
+        <v>535547</v>
       </c>
       <c r="R2" t="n">
-        <v>6393765.578481792</v>
+        <v>6393733</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1971-06-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1971-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observatör: Gunvald Bruce. &gt;10.</t>
+          <t>16 stubbar, 3 lågor undersökta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,20 +776,151 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Granskog ca 40-50 år, god status på miljön för arten</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>låga # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>585329</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105117</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spindelört</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Thesium alpinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rumskulla, 600 m N om kyrkan, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>535572</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6393766</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rumskulla</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Arkiv-Hf-Vim-0195</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1971-06-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1971-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observatör: Gunvald Bruce. &gt;10.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Åke Rühling</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Åke Rühling</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
